--- a/r4-core-96-dead-code-removal/StructureDefinition-at-core-organization.xlsx
+++ b/r4-core-96-dead-code-removal/StructureDefinition-at-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3473" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3185" uniqueCount="429">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:26:41+00:00</t>
+    <t>2024-11-22T08:22:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -501,6 +501,15 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>Organization.identifier:GDA-OID</t>
+  </si>
+  <si>
+    <t>GDA-OID</t>
+  </si>
+  <si>
+    <t>Organization.identifier:GDA-OID.id</t>
+  </si>
+  <si>
     <t>Organization.identifier.id</t>
   </si>
   <si>
@@ -520,6 +529,9 @@
     <t>n/a</t>
   </si>
   <si>
+    <t>Organization.identifier:GDA-OID.extension</t>
+  </si>
+  <si>
     <t>Organization.identifier.extension</t>
   </si>
   <si>
@@ -536,6 +548,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>Organization.identifier:GDA-OID.use</t>
+  </si>
+  <si>
     <t>Organization.identifier.use</t>
   </si>
   <si>
@@ -564,6 +579,9 @@
   </si>
   <si>
     <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Organization.identifier:GDA-OID.type</t>
   </si>
   <si>
     <t>Organization.identifier.type</t>
@@ -588,7 +606,10 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet/hl7-at-patientidentifier</t>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -597,10 +618,13 @@
     <t>CX.5</t>
   </si>
   <si>
+    <t>Organization.identifier:GDA-OID.system</t>
+  </si>
+  <si>
     <t>Organization.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
+    <t>A GDA in Austria is represented via an URI (OID)</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -612,6 +636,9 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>urn:ietf:rfc:3986</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
@@ -627,10 +654,13 @@
     <t>./IdentifierType</t>
   </si>
   <si>
+    <t>Organization.identifier:GDA-OID.value</t>
+  </si>
+  <si>
     <t>Organization.identifier.value</t>
   </si>
   <si>
-    <t>The value that is unique</t>
+    <t>OID for the GDA in Austria</t>
   </si>
   <si>
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
@@ -652,6 +682,9 @@
   </si>
   <si>
     <t>./Value</t>
+  </si>
+  <si>
+    <t>Organization.identifier:GDA-OID.period</t>
   </si>
   <si>
     <t>Organization.identifier.period</t>
@@ -679,6 +712,9 @@
     <t>./StartDate and ./EndDate</t>
   </si>
   <si>
+    <t>Organization.identifier:GDA-OID.assigner</t>
+  </si>
+  <si>
     <t>Organization.identifier.assigner</t>
   </si>
   <si>
@@ -705,51 +741,6 @@
   </si>
   <si>
     <t>./IdentifierIssuingAuthority</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID</t>
-  </si>
-  <si>
-    <t>GDA-OID</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID.use</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID.type</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID.system</t>
-  </si>
-  <si>
-    <t>A GDA in Austria is represented via an URI (OID)</t>
-  </si>
-  <si>
-    <t>urn:ietf:rfc:3986</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID.value</t>
-  </si>
-  <si>
-    <t>OID for the GDA in Austria</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID.period</t>
-  </si>
-  <si>
-    <t>Organization.identifier:GDA-OID.assigner</t>
   </si>
   <si>
     <t>Organization.identifier:GDA-OID.assigner.id</t>
@@ -884,6 +875,9 @@
   </si>
   <si>
     <t>Organization.identifier:VPNR.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
   </si>
   <si>
     <t>Organization.identifier:VPNR.period</t>
@@ -1660,7 +1654,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN95"/>
+  <dimension ref="A1:AN87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.25390625" customWidth="true" bestFit="true"/>
@@ -2967,9 +2961,11 @@
         <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>21</v>
       </c>
@@ -2987,19 +2983,21 @@
         <v>21</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="O12" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>21</v>
       </c>
@@ -3047,50 +3045,50 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
@@ -3102,17 +3100,15 @@
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
@@ -3149,37 +3145,37 @@
         <v>21</v>
       </c>
       <c r="AB13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>21</v>
@@ -3190,46 +3186,44 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
       </c>
@@ -3253,49 +3247,49 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>174</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>21</v>
@@ -3306,10 +3300,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3326,25 +3320,25 @@
         <v>21</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>178</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -3369,11 +3363,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3391,7 +3387,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3406,10 +3402,10 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>186</v>
+        <v>130</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
@@ -3420,10 +3416,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3446,19 +3442,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>101</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="O16" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -3471,43 +3467,43 @@
         <v>21</v>
       </c>
       <c r="T16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3522,13 +3518,13 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>21</v>
@@ -3536,10 +3532,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3547,7 +3543,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>87</v>
@@ -3562,24 +3558,26 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>157</v>
+        <v>101</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="N17" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>21</v>
@@ -3653,7 +3651,7 @@
         <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3661,7 +3659,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>87</v>
@@ -3676,7 +3674,7 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>207</v>
+        <v>160</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>208</v>
@@ -3684,7 +3682,9 @@
       <c r="M18" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="N18" s="2"/>
+      <c r="N18" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3697,7 +3697,7 @@
         <v>21</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>21</v>
@@ -3733,7 +3733,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3748,13 +3748,13 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>21</v>
@@ -3762,10 +3762,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3788,17 +3788,15 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3847,7 +3845,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3862,13 +3860,13 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>21</v>
@@ -3876,14 +3874,12 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>21</v>
       </c>
@@ -3904,18 +3900,18 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>146</v>
+        <v>228</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -3963,39 +3959,39 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>144</v>
+        <v>231</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>153</v>
+        <v>233</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>156</v>
+        <v>236</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4018,13 +4014,13 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4075,7 +4071,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4093,7 +4089,7 @@
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>21</v>
@@ -4104,10 +4100,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4136,7 +4132,7 @@
         <v>134</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>136</v>
@@ -4177,10 +4173,10 @@
         <v>21</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>21</v>
@@ -4189,7 +4185,7 @@
         <v>150</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4207,7 +4203,7 @@
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>21</v>
@@ -4218,10 +4214,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>167</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4238,26 +4234,24 @@
         <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>168</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>169</v>
+        <v>242</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
       </c>
@@ -4281,13 +4275,13 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>174</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4305,7 +4299,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4314,16 +4308,16 @@
         <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -4334,10 +4328,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>177</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4360,20 +4354,18 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>180</v>
+        <v>249</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4397,13 +4389,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4421,7 +4413,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4436,10 +4428,10 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
@@ -4450,10 +4442,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>187</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4461,7 +4453,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>87</v>
@@ -4476,32 +4468,30 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>233</v>
+        <v>21</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>21</v>
@@ -4537,7 +4527,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>193</v>
+        <v>259</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4552,13 +4542,13 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>21</v>
@@ -4566,10 +4556,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>197</v>
+        <v>262</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4577,7 +4567,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>87</v>
@@ -4592,16 +4582,16 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>200</v>
+        <v>265</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4609,13 +4599,13 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>21</v>
+        <v>266</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>21</v>
@@ -4651,7 +4641,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>202</v>
+        <v>267</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4666,13 +4656,13 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>21</v>
@@ -4680,12 +4670,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>21</v>
       </c>
@@ -4694,7 +4686,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
@@ -4706,16 +4698,18 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>207</v>
+        <v>145</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>208</v>
+        <v>146</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>209</v>
+        <v>147</v>
       </c>
       <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -4763,39 +4757,39 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>210</v>
+        <v>144</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>211</v>
+        <v>152</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>212</v>
+        <v>153</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>213</v>
+        <v>154</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4815,20 +4809,18 @@
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>216</v>
+        <v>161</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4877,7 +4869,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>219</v>
+        <v>163</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4889,16 +4881,16 @@
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>220</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>221</v>
+        <v>164</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>21</v>
@@ -4906,21 +4898,21 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>238</v>
+        <v>271</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>239</v>
+        <v>166</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -4932,15 +4924,17 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -4977,37 +4971,37 @@
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
@@ -5018,44 +5012,46 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>241</v>
+        <v>172</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5079,49 +5075,49 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>21</v>
+        <v>178</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
@@ -5132,10 +5128,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>243</v>
+        <v>183</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5158,18 +5154,20 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>244</v>
+        <v>185</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>245</v>
+        <v>186</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5193,13 +5191,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -5217,7 +5215,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5226,16 +5224,16 @@
         <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>130</v>
+        <v>181</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
@@ -5246,10 +5244,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5257,7 +5255,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>87</v>
@@ -5275,27 +5273,29 @@
         <v>101</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>252</v>
+        <v>197</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>21</v>
@@ -5307,13 +5307,13 @@
         <v>21</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>254</v>
+        <v>21</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>255</v>
+        <v>21</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5331,7 +5331,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>256</v>
+        <v>202</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5346,13 +5346,13 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>21</v>
@@ -5360,10 +5360,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>258</v>
+        <v>207</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>87</v>
@@ -5386,16 +5386,16 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>261</v>
+        <v>210</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5409,7 +5409,7 @@
         <v>21</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>21</v>
@@ -5445,7 +5445,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5460,13 +5460,13 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>263</v>
+        <v>214</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>21</v>
+        <v>215</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>21</v>
@@ -5474,10 +5474,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>265</v>
+        <v>217</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5500,24 +5500,22 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>157</v>
+        <v>218</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>266</v>
+        <v>219</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>21</v>
@@ -5559,7 +5557,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>270</v>
+        <v>221</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5574,13 +5572,13 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>130</v>
+        <v>223</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>21</v>
@@ -5588,14 +5586,12 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>21</v>
       </c>
@@ -5604,7 +5600,7 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>21</v>
@@ -5616,18 +5612,18 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>146</v>
+        <v>228</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -5675,39 +5671,39 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>144</v>
+        <v>231</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>153</v>
+        <v>233</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>156</v>
+        <v>236</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5730,13 +5726,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5787,7 +5783,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5805,7 +5801,7 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
@@ -5816,10 +5812,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5848,7 +5844,7 @@
         <v>134</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>136</v>
@@ -5889,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>21</v>
@@ -5901,7 +5897,7 @@
         <v>150</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5919,7 +5915,7 @@
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
@@ -5930,10 +5926,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>167</v>
+        <v>240</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5950,26 +5946,24 @@
         <v>21</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>168</v>
+        <v>241</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>169</v>
+        <v>242</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -5993,13 +5987,13 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>174</v>
+        <v>21</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6017,7 +6011,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6026,16 +6020,16 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
@@ -6046,10 +6040,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>177</v>
+        <v>247</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6072,20 +6066,18 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>180</v>
+        <v>249</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
       </c>
@@ -6109,13 +6101,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6133,7 +6125,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6148,10 +6140,10 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
@@ -6162,10 +6154,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>187</v>
+        <v>255</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6173,7 +6165,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>87</v>
@@ -6188,32 +6180,30 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>21</v>
@@ -6249,7 +6239,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>193</v>
+        <v>259</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6264,13 +6254,13 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6278,10 +6268,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>197</v>
+        <v>262</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6289,7 +6279,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>87</v>
@@ -6304,16 +6294,16 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>198</v>
+        <v>263</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>200</v>
+        <v>265</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6321,13 +6311,13 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>21</v>
+        <v>287</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>21</v>
@@ -6363,7 +6353,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>202</v>
+        <v>267</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6378,13 +6368,13 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
@@ -6392,12 +6382,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="D42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6418,16 +6410,18 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>207</v>
+        <v>145</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>208</v>
+        <v>146</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>209</v>
+        <v>147</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6475,39 +6469,39 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>210</v>
+        <v>144</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>211</v>
+        <v>152</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>212</v>
+        <v>153</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>213</v>
+        <v>154</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6527,20 +6521,18 @@
         <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>216</v>
+        <v>161</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6589,7 +6581,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>219</v>
+        <v>163</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6601,16 +6593,16 @@
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>220</v>
+        <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>221</v>
+        <v>164</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -6618,21 +6610,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>239</v>
+        <v>166</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -6644,15 +6636,17 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6689,37 +6683,37 @@
         <v>21</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
@@ -6730,44 +6724,46 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>241</v>
+        <v>172</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -6791,49 +6787,49 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>21</v>
+        <v>178</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
@@ -6844,10 +6840,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>243</v>
+        <v>183</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6870,18 +6866,20 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>244</v>
+        <v>185</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>245</v>
+        <v>186</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -6905,13 +6903,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -6929,7 +6927,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6938,16 +6936,16 @@
         <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>130</v>
+        <v>181</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
@@ -6958,10 +6956,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6969,7 +6967,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>87</v>
@@ -6987,27 +6985,29 @@
         <v>101</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>252</v>
+        <v>197</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>21</v>
+        <v>296</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>21</v>
@@ -7019,13 +7019,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>254</v>
+        <v>21</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>255</v>
+        <v>21</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7043,7 +7043,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>256</v>
+        <v>202</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7058,13 +7058,13 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7072,10 +7072,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>258</v>
+        <v>207</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>87</v>
@@ -7098,16 +7098,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>261</v>
+        <v>210</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7121,7 +7121,7 @@
         <v>21</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>21</v>
@@ -7157,7 +7157,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7172,13 +7172,13 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>263</v>
+        <v>214</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>21</v>
+        <v>215</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7186,10 +7186,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>265</v>
+        <v>217</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7212,24 +7212,22 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>157</v>
+        <v>218</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>266</v>
+        <v>219</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>289</v>
+        <v>21</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>21</v>
@@ -7271,7 +7269,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>270</v>
+        <v>221</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7286,13 +7284,13 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>130</v>
+        <v>223</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7300,14 +7298,12 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7328,18 +7324,18 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>146</v>
+        <v>228</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7387,39 +7383,39 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>144</v>
+        <v>231</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>153</v>
+        <v>233</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>156</v>
+        <v>236</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7442,13 +7438,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7499,7 +7495,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7517,7 +7513,7 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
@@ -7528,10 +7524,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7560,7 +7556,7 @@
         <v>134</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>136</v>
@@ -7601,10 +7597,10 @@
         <v>21</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>21</v>
@@ -7613,7 +7609,7 @@
         <v>150</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7631,7 +7627,7 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
@@ -7642,10 +7638,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>167</v>
+        <v>240</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7662,26 +7658,24 @@
         <v>21</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>168</v>
+        <v>241</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>169</v>
+        <v>242</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -7705,13 +7699,13 @@
         <v>21</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>174</v>
+        <v>21</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -7729,7 +7723,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7738,16 +7732,16 @@
         <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>21</v>
@@ -7758,10 +7752,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>177</v>
+        <v>247</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7784,20 +7778,18 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>180</v>
+        <v>249</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -7821,13 +7813,13 @@
         <v>21</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -7845,7 +7837,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7860,10 +7852,10 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
@@ -7874,10 +7866,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>187</v>
+        <v>255</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7885,7 +7877,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>87</v>
@@ -7900,32 +7892,30 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>297</v>
+        <v>256</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>298</v>
+        <v>21</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>21</v>
@@ -7961,7 +7951,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>193</v>
+        <v>259</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7976,13 +7966,13 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -7990,10 +7980,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>197</v>
+        <v>262</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8001,7 +7991,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>87</v>
@@ -8016,16 +8006,16 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>198</v>
+        <v>263</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>200</v>
+        <v>265</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8033,13 +8023,13 @@
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>21</v>
+        <v>306</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>21</v>
@@ -8075,7 +8065,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>202</v>
+        <v>267</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8090,13 +8080,13 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8104,12 +8094,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="D57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8130,16 +8122,18 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>207</v>
+        <v>145</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>208</v>
+        <v>146</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>209</v>
+        <v>147</v>
       </c>
       <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8187,39 +8181,39 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>210</v>
+        <v>144</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>211</v>
+        <v>152</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>212</v>
+        <v>153</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>213</v>
+        <v>154</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8239,20 +8233,18 @@
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>216</v>
+        <v>161</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8301,7 +8293,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>219</v>
+        <v>163</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8313,16 +8305,16 @@
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>220</v>
+        <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>221</v>
+        <v>164</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -8330,21 +8322,21 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>239</v>
+        <v>166</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -8356,15 +8348,17 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8401,37 +8395,37 @@
         <v>21</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
@@ -8442,44 +8436,46 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>241</v>
+        <v>172</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -8503,49 +8499,49 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>21</v>
+        <v>178</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
@@ -8556,10 +8552,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>243</v>
+        <v>183</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8582,18 +8578,20 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>244</v>
+        <v>185</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>245</v>
+        <v>186</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -8617,13 +8615,13 @@
         <v>21</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>21</v>
@@ -8641,7 +8639,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8650,16 +8648,16 @@
         <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>130</v>
+        <v>181</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
@@ -8670,10 +8668,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8681,7 +8679,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>87</v>
@@ -8699,27 +8697,29 @@
         <v>101</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>251</v>
+        <v>314</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>252</v>
+        <v>197</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>21</v>
+        <v>315</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>21</v>
@@ -8731,13 +8731,13 @@
         <v>21</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>254</v>
+        <v>21</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>255</v>
+        <v>21</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>21</v>
@@ -8755,7 +8755,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>256</v>
+        <v>202</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8770,13 +8770,13 @@
         <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -8784,10 +8784,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>258</v>
+        <v>207</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>87</v>
@@ -8810,16 +8810,16 @@
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>259</v>
+        <v>317</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>261</v>
+        <v>210</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8833,7 +8833,7 @@
         <v>21</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>21</v>
@@ -8869,7 +8869,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8884,13 +8884,13 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>263</v>
+        <v>214</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>21</v>
+        <v>215</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -8898,10 +8898,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>265</v>
+        <v>217</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8924,24 +8924,22 @@
         <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>157</v>
+        <v>218</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>266</v>
+        <v>219</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>308</v>
+        <v>21</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>21</v>
@@ -8983,7 +8981,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>270</v>
+        <v>221</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8998,13 +8996,13 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>130</v>
+        <v>223</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
@@ -9012,14 +9010,12 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9040,18 +9036,18 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>146</v>
+        <v>228</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9099,39 +9095,39 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>144</v>
+        <v>231</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>153</v>
+        <v>233</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>156</v>
+        <v>236</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9154,13 +9150,13 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9211,7 +9207,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9229,7 +9225,7 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>21</v>
@@ -9240,10 +9236,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9272,7 +9268,7 @@
         <v>134</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>136</v>
@@ -9313,10 +9309,10 @@
         <v>21</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>21</v>
@@ -9325,7 +9321,7 @@
         <v>150</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9343,7 +9339,7 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>21</v>
@@ -9354,10 +9350,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>167</v>
+        <v>240</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9374,26 +9370,24 @@
         <v>21</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>168</v>
+        <v>241</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>169</v>
+        <v>242</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>21</v>
       </c>
@@ -9417,13 +9411,13 @@
         <v>21</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>174</v>
+        <v>21</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>21</v>
@@ -9441,7 +9435,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9450,16 +9444,16 @@
         <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>21</v>
+        <v>245</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL68" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>21</v>
@@ -9470,10 +9464,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>177</v>
+        <v>247</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9496,20 +9490,18 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>180</v>
+        <v>249</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -9533,13 +9525,13 @@
         <v>21</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -9557,7 +9549,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9572,10 +9564,10 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>21</v>
@@ -9586,10 +9578,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>187</v>
+        <v>255</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9597,7 +9589,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>87</v>
@@ -9612,32 +9604,30 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>316</v>
+        <v>256</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>317</v>
+        <v>21</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>21</v>
@@ -9673,7 +9663,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>193</v>
+        <v>259</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9688,13 +9678,13 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>195</v>
+        <v>260</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
@@ -9702,10 +9692,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>197</v>
+        <v>262</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9713,7 +9703,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>87</v>
@@ -9728,16 +9718,16 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>319</v>
+        <v>263</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>200</v>
+        <v>265</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9745,13 +9735,13 @@
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>21</v>
+        <v>326</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>21</v>
@@ -9787,7 +9777,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>202</v>
+        <v>267</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9802,13 +9792,13 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
@@ -9816,10 +9806,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>206</v>
+        <v>327</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9836,26 +9826,32 @@
         <v>21</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>207</v>
+        <v>328</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>208</v>
+        <v>329</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q72" s="2"/>
+      <c r="Q72" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="R72" t="s" s="2">
         <v>21</v>
       </c>
@@ -9899,7 +9895,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>210</v>
+        <v>327</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9914,24 +9910,24 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>211</v>
+        <v>334</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>212</v>
+        <v>335</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>213</v>
+        <v>336</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>21</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>214</v>
+        <v>338</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9942,7 +9938,7 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>21</v>
@@ -9954,18 +9950,20 @@
         <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>216</v>
+        <v>339</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>217</v>
+        <v>340</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
       </c>
@@ -9989,13 +9987,11 @@
         <v>21</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>21</v>
+        <v>343</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>21</v>
@@ -10013,13 +10009,13 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>219</v>
+        <v>338</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
@@ -10028,24 +10024,24 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>220</v>
+        <v>344</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>221</v>
+        <v>345</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>222</v>
+        <v>164</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>21</v>
+        <v>346</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>239</v>
+        <v>347</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10065,19 +10061,23 @@
         <v>21</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>158</v>
+        <v>348</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
       </c>
@@ -10125,7 +10125,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>160</v>
+        <v>347</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10134,19 +10134,19 @@
         <v>87</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>21</v>
+        <v>352</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>161</v>
+        <v>353</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>21</v>
+        <v>354</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10154,14 +10154,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>323</v>
+        <v>355</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>241</v>
+        <v>355</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>132</v>
+        <v>21</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10180,18 +10180,20 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>134</v>
+        <v>356</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>163</v>
+        <v>357</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
       </c>
@@ -10227,19 +10229,19 @@
         <v>21</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>166</v>
+        <v>355</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10251,13 +10253,13 @@
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>161</v>
+        <v>353</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>21</v>
@@ -10268,10 +10270,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>243</v>
+        <v>360</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10282,7 +10284,7 @@
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>21</v>
@@ -10291,21 +10293,23 @@
         <v>21</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>157</v>
+        <v>361</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>244</v>
+        <v>362</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>245</v>
+        <v>363</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
@@ -10353,28 +10357,28 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>247</v>
+        <v>360</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>248</v>
+        <v>366</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>99</v>
+        <v>367</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>21</v>
+        <v>368</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>130</v>
+        <v>369</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>21</v>
+        <v>370</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -10382,10 +10386,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>325</v>
+        <v>371</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>250</v>
+        <v>371</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10396,7 +10400,7 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>21</v>
@@ -10405,21 +10409,23 @@
         <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>101</v>
+        <v>372</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>251</v>
+        <v>373</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>252</v>
+        <v>374</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>21</v>
       </c>
@@ -10443,13 +10449,13 @@
         <v>21</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>254</v>
+        <v>21</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>255</v>
+        <v>21</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>21</v>
@@ -10467,28 +10473,28 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>256</v>
+        <v>371</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>99</v>
+        <v>378</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>21</v>
+        <v>379</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>130</v>
+        <v>380</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>21</v>
+        <v>381</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
@@ -10496,10 +10502,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>326</v>
+        <v>382</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>258</v>
+        <v>382</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10522,18 +10528,18 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>259</v>
+        <v>383</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
       </c>
@@ -10581,7 +10587,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>262</v>
+        <v>382</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10596,13 +10602,13 @@
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>21</v>
+        <v>334</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>263</v>
+        <v>386</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
@@ -10610,10 +10616,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>327</v>
+        <v>387</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>265</v>
+        <v>387</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10624,7 +10630,7 @@
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>21</v>
@@ -10633,27 +10639,29 @@
         <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>157</v>
+        <v>388</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>266</v>
+        <v>389</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>267</v>
+        <v>390</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>328</v>
+        <v>21</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>21</v>
@@ -10695,13 +10703,13 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>270</v>
+        <v>387</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>21</v>
@@ -10713,7 +10721,7 @@
         <v>21</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>130</v>
+        <v>393</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>21</v>
@@ -10724,10 +10732,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>329</v>
+        <v>394</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>329</v>
+        <v>394</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10744,32 +10752,26 @@
         <v>21</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>330</v>
+        <v>160</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>331</v>
+        <v>161</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q80" t="s" s="2">
-        <v>335</v>
-      </c>
+      <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
         <v>21</v>
       </c>
@@ -10813,7 +10815,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>329</v>
+        <v>163</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10825,31 +10827,31 @@
         <v>21</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>336</v>
+        <v>21</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>337</v>
+        <v>164</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>338</v>
+        <v>21</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>339</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>340</v>
+        <v>395</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>340</v>
+        <v>395</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -10865,23 +10867,21 @@
         <v>21</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>341</v>
+        <v>134</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>342</v>
+        <v>167</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>21</v>
       </c>
@@ -10905,11 +10905,13 @@
         <v>21</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y81" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z81" t="s" s="2">
-        <v>345</v>
+        <v>21</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>21</v>
@@ -10927,7 +10929,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>340</v>
+        <v>170</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10939,62 +10941,62 @@
         <v>21</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>346</v>
+        <v>21</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>347</v>
+        <v>164</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>348</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>349</v>
+        <v>396</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>349</v>
+        <v>396</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>21</v>
+        <v>397</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>350</v>
+        <v>398</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>351</v>
+        <v>399</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>352</v>
+        <v>136</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>353</v>
+        <v>142</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -11043,28 +11045,28 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>349</v>
+        <v>400</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>354</v>
+        <v>21</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>355</v>
+        <v>130</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>356</v>
+        <v>21</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
@@ -11072,10 +11074,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>357</v>
+        <v>401</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>357</v>
+        <v>401</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11086,7 +11088,7 @@
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>21</v>
@@ -11098,19 +11100,17 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>358</v>
+        <v>402</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>361</v>
+        <v>404</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -11135,13 +11135,13 @@
         <v>21</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>21</v>
+        <v>405</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>21</v>
+        <v>406</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>21</v>
@@ -11159,13 +11159,13 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>357</v>
+        <v>401</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>21</v>
@@ -11177,7 +11177,7 @@
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>21</v>
@@ -11188,10 +11188,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>362</v>
+        <v>408</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>362</v>
+        <v>408</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11202,7 +11202,7 @@
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>21</v>
@@ -11214,19 +11214,17 @@
         <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>363</v>
+        <v>409</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>364</v>
+        <v>410</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>367</v>
+        <v>412</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
@@ -11275,28 +11273,28 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>362</v>
+        <v>408</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>368</v>
+        <v>21</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>369</v>
+        <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>370</v>
+        <v>413</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>371</v>
+        <v>414</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>372</v>
+        <v>21</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
@@ -11304,10 +11302,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>373</v>
+        <v>415</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>373</v>
+        <v>415</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11330,19 +11328,17 @@
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>375</v>
+        <v>416</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>378</v>
+        <v>418</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>21</v>
@@ -11391,7 +11387,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>373</v>
+        <v>415</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11400,19 +11396,19 @@
         <v>79</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>379</v>
+        <v>21</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>380</v>
+        <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>381</v>
+        <v>419</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>382</v>
+        <v>420</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>383</v>
+        <v>21</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
@@ -11420,10 +11416,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>384</v>
+        <v>421</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>384</v>
+        <v>421</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11443,20 +11439,22 @@
         <v>21</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>215</v>
+        <v>372</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="O86" t="s" s="2">
-        <v>387</v>
+        <v>422</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>21</v>
@@ -11505,7 +11503,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>384</v>
+        <v>421</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11514,19 +11512,19 @@
         <v>87</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>99</v>
+        <v>423</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>336</v>
+        <v>379</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>161</v>
+        <v>381</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>21</v>
@@ -11534,10 +11532,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>389</v>
+        <v>424</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>389</v>
+        <v>424</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11560,19 +11558,17 @@
         <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>390</v>
+        <v>425</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>391</v>
+        <v>426</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>21</v>
@@ -11621,7 +11617,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>389</v>
+        <v>424</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11639,926 +11635,12 @@
         <v>21</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>395</v>
+        <v>164</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
-      <c r="P88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O89" s="2"/>
-      <c r="P89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="P90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="P91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="P92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="P93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="P94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="P95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN95" t="s" s="2">
         <v>21</v>
       </c>
     </row>
